--- a/templates/Invoice-Template.xlsx
+++ b/templates/Invoice-Template.xlsx
@@ -2248,12 +2248,7 @@
     <row r="18" ht="38.5" customFormat="1" customHeight="1" s="2">
       <c r="A18" s="32" t="n"/>
       <c r="B18" s="72" t="n"/>
-      <c r="C18" s="39" t="inlineStr">
-        <is>
-          <t>總付款金額為柒仟壹佰美元
-Full payment of USD, 7,100</t>
-        </is>
-      </c>
+      <c r="C18" s="39" t="inlineStr"/>
       <c r="D18" s="81" t="n"/>
       <c r="E18" s="82" t="n"/>
       <c r="F18" s="83" t="n"/>

--- a/templates/Invoice-Template.xlsx
+++ b/templates/Invoice-Template.xlsx
@@ -1925,7 +1925,9 @@
       <c r="F1" s="67" t="n"/>
       <c r="G1" s="67" t="n"/>
     </row>
-    <row r="2" ht="4.5" customHeight="1" s="65"/>
+    <row r="2" ht="4.5" customHeight="1" s="65">
+      <c r="A2" t="inlineStr"/>
+    </row>
     <row r="3" ht="52" customFormat="1" customHeight="1" s="1">
       <c r="A3" s="6" t="inlineStr">
         <is>

--- a/templates/Invoice-Template.xlsx
+++ b/templates/Invoice-Template.xlsx
@@ -1926,7 +1926,11 @@
       <c r="G1" s="67" t="n"/>
     </row>
     <row r="2" ht="4.5" customHeight="1" s="65">
-      <c r="A2" t="inlineStr"/>
+      <c r="A2" s="0" t="inlineStr">
+        <is>
+          <t>VERSION 2024-07</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="52" customFormat="1" customHeight="1" s="1">
       <c r="A3" s="6" t="inlineStr">

--- a/templates/Invoice-Template.xlsx
+++ b/templates/Invoice-Template.xlsx
@@ -1926,11 +1926,7 @@
       <c r="G1" s="67" t="n"/>
     </row>
     <row r="2" ht="4.5" customHeight="1" s="65">
-      <c r="A2" s="0" t="inlineStr">
-        <is>
-          <t>VERSION 2024-07</t>
-        </is>
-      </c>
+      <c r="A2" s="0" t="inlineStr"/>
     </row>
     <row r="3" ht="52" customFormat="1" customHeight="1" s="1">
       <c r="A3" s="6" t="inlineStr">
